--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>群組值集：組合 Core 之檢驗子集（VS-CoreDataset）、生理量測（VS-TWHAVitalSigns）與社會史碼，具體化主管機關（國健署）制定之最小共通上傳集（原案 16 主項／21 列，對標 USCDI regulator-defined minimum）。僅供文件與完整度／覆蓋矩陣機器核對，不作 Observation.code 綁定。嚼檳量／嚼檳月數屬本地 Extension（ext-betelnut-quantity），無國際碼，於文件註記。</t>
+    <t>群組值集：組合 Core 之檢驗子集（VS-CoreDataset）、生理量測（VS-TWHAVitalSigns）與社會史碼，具體化主管機關（國健署）制定之最小共通上傳集（原案 16 主項／21 列，對標 USCDI regulator-defined minimum）。僅供文件與完整度／覆蓋矩陣機器核對，不作 Observation.code 綁定。嚼檳之量／年／戒除年由臺灣癌症登記短表 IG（TWCR_SF, fhir.TWCRSF#0.1.1）之值集承載（sf-BetNutChewAmount／sf-BetNutChewYear／sf-BetNutChewQuit，required 綁定，見 TWHA-SocialHistory-BetelNut），非本 IG 自訂，亦非無碼；LOINC／SNOMED 就此無對應碼故採國內值集。注意上游以「年」計，與吸菸之戒除「月數」（LNC#63632-4）單位不同。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>群組值集：組合 Core 之檢驗子集（VS-CoreDataset）、生理量測（VS-TWHAVitalSigns）與社會史碼，具體化主管機關（國健署）制定之最小共通上傳集（原案 16 主項／21 列，對標 USCDI regulator-defined minimum）。僅供文件與完整度／覆蓋矩陣機器核對，不作 Observation.code 綁定。嚼檳之量／年／戒除年由臺灣癌症登記短表 IG（TWCR_SF, fhir.TWCRSF#0.1.1）之值集承載（sf-BetNutChewAmount／sf-BetNutChewYear／sf-BetNutChewQuit，required 綁定，見 TWHA-SocialHistory-BetelNut），非本 IG 自訂，亦非無碼；LOINC／SNOMED 就此無對應碼故採國內值集。注意上游以「年」計，與吸菸之戒除「月數」（LNC#63632-4）單位不同。</t>
+    <t>群組值集：組合 Core 之檢驗子集（VS-CoreDataset）、生理量測（VS-TWHAVitalSigns）與社會史碼，具體化主管機關（國健署）制定之最小共通上傳集（原案 16 主項／21 列，對標 USCDI regulator-defined minimum）。僅供文件與完整度／覆蓋矩陣機器核對，不作 Observation.code 綁定。嚼檳之狀態由本 IG 之 VS-BetelNutStatus 承載（與吸菸狀態四碼逐碼對稱）；量／年數／戒除期間自 v0.4.0 起改以 UCUM Quantity 承載（{quid}/d、a、a 或 mo），上游臺灣癌症登記短表 IG（TWCR_SF, fhir.TWCRSF#0.1.1）之級距碼降為可選 component（extensible）供勾稽之用，見 TWHA-SocialHistory-BetelNut 與術語頁 §6.2b。注意戒除期間之單位以原始採集粒度為準（上游以「年」計），與吸菸之戒除「月數」（LNC#63632-4）不同，不得逕行換算。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>群組值集：組合 Core 之檢驗子集（VS-CoreDataset）、生理量測（VS-TWHAVitalSigns）與社會史碼，具體化主管機關（國健署）制定之最小共通上傳集（原案 16 主項／21 列，對標 USCDI regulator-defined minimum）。僅供文件與完整度／覆蓋矩陣機器核對，不作 Observation.code 綁定。嚼檳之狀態由本 IG 之 VS-BetelNutStatus 承載（與吸菸狀態四碼逐碼對稱）；量／年數／戒除期間自 v0.4.0 起改以 UCUM Quantity 承載（{quid}/d、a、a 或 mo），上游臺灣癌症登記短表 IG（TWCR_SF, fhir.TWCRSF#0.1.1）之級距碼降為可選 component（extensible）供勾稽之用，見 TWHA-SocialHistory-BetelNut 與術語頁 §6.2b。注意戒除期間之單位以原始採集粒度為準（上游以「年」計），與吸菸之戒除「月數」（LNC#63632-4）不同，不得逕行換算。</t>
+    <t>【主管機關：國民健康署】群組值集：組合 Core 之檢驗子集（VS-CoreDataset）、生理量測（VS-TWHAVitalSigns）與社會史碼，具體化主管機關（國健署）制定之最小共通上傳集（原案 16 主項／21 列，對標 USCDI regulator-defined minimum）。僅供文件與完整度／覆蓋矩陣機器核對，不作 Observation.code 綁定。嚼檳之狀態由本 IG 之 VS-BetelNutStatus 承載（與吸菸狀態四碼逐碼對稱）；量／年數／戒除期間自 v0.4.0 起改以 UCUM Quantity 承載（{quid}/d、a、a 或 mo），上游臺灣癌症登記短表 IG（TWCR_SF, fhir.TWCRSF#0.1.1）之級距碼降為可選 component（extensible）供勾稽之用，見 TWHA-SocialHistory-BetelNut 與術語頁 §6.2b。注意戒除期間之單位以原始採集粒度為準（上游以「年」計），與吸菸之戒除「月數」（LNC#63632-4）不同，不得逕行換算。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,10 +132,10 @@
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>698188003</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
+    <t>betel-quid-chewing-status</t>
+  </si>
+  <si>
+    <t>https://twcore.mohw.gov.tw/ig/twha/CodeSystem/CS-BetelNutObservable</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -11,12 +11,13 @@
     <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Exclude #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,6 +137,9 @@
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twha/CodeSystem/CS-BetelNutObservable</t>
+  </si>
+  <si>
+    <t>39156-5</t>
   </si>
 </sst>
 </file>
@@ -551,4 +555,48 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreUploadSet.xlsx
+++ b/ValueSet-VS-CoreUploadSet.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
